--- a/downloads/FRB_H10_latest.xlsx
+++ b/downloads/FRB_H10_latest.xlsx
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -55,11 +53,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -453,7 +450,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-28 to 2026-10-02</t>
+          <t>2026-10-05 to 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -514,141 +511,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>0.702</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>1.1367</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>1.3257</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0.5668</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>1.4169</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>95.98</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>4.0805</v>
+          <t>2026-10-05</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>0.6979</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>1.1336</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>1.3212</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0.5635</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>1.4189</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>95.98</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>4.0798</v>
+          <t>2026-10-06</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>0.6952</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>1.1345</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>1.3267</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>0.5639999999999999</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>1.421</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>95.83</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>4.0775</v>
+          <t>2026-10-07</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>0.6911</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>1.1232</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>1.3196</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>1.4253</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>96.31999999999999</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>4.082</v>
+          <t>2026-10-08</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>0.6953</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>1.1259</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>1.3234</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>0.5612</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>1.4253</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>96.31</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>4.081</v>
+          <t>2026-10-09</t>
+        </is>
       </c>
     </row>
     <row r="13">

--- a/downloads/FRB_H10_latest.xlsx
+++ b/downloads/FRB_H10_latest.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -53,10 +55,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -514,6 +517,27 @@
           <t>2026-10-05</t>
         </is>
       </c>
+      <c r="B6" s="3" t="n">
+        <v>0.6969</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1.1211</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1.3217</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.5598</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>1.4244</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>96.29000000000001</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>4.085</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -521,6 +545,27 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="B7" s="3" t="n">
+        <v>0.6984</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1.1262</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1.3281</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.5626</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>1.4219</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>96.42</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>4.0825</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -528,6 +573,27 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="B8" s="3" t="n">
+        <v>0.6962</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1.1187</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>1.3213</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0.5597</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>1.4255</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>96.76000000000001</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>4.086</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -535,12 +601,54 @@
           <t>2026-10-08</t>
         </is>
       </c>
+      <c r="B9" s="3" t="n">
+        <v>0.6949</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1.1192</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>1.3211</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0.5594</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>1.4246</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>96.78</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>4.089</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0.6979</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>1.1193</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1.3229</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0.5611</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>1.4269</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>96.73</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>4.083</v>
       </c>
     </row>
     <row r="13">

--- a/downloads/FRB_H10_latest.xlsx
+++ b/downloads/FRB_H10_latest.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-05 to 2026-10-09</t>
+          <t>2026-10-12 to 2026-10-16</t>
         </is>
       </c>
     </row>
@@ -514,141 +514,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>0.6969</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>1.1211</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>1.3217</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0.5598</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>1.4244</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>96.29000000000001</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>4.085</v>
+          <t>2026-10-12</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
         <v>0.6984</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1.1262</v>
+        <v>1.1196</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1.3281</v>
+        <v>1.3255</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.5626</v>
+        <v>0.5616</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.4219</v>
+        <v>1.4214</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>96.42</v>
+        <v>95.28</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>4.0825</v>
+        <v>4.0839</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.6962</v>
+        <v>0.6956</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1.1187</v>
+        <v>1.1123</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.3213</v>
+        <v>1.3155</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.5597</v>
+        <v>0.5572</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.4255</v>
+        <v>1.4273</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>96.76000000000001</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>4.086</v>
+        <v>4.081</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.6949</v>
+        <v>0.6914</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1.1192</v>
+        <v>1.1204</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1.3211</v>
+        <v>1.3257</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.5594</v>
+        <v>0.5607</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.4246</v>
+        <v>1.4197</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>96.78</v>
+        <v>95.06</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>4.089</v>
+        <v>4.0799</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.6979</v>
+        <v>0.695</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1.1193</v>
+        <v>1.1231</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.3229</v>
+        <v>1.333</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.5611</v>
+        <v>0.5654</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.4269</v>
+        <v>1.4157</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>96.73</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>4.083</v>
+        <v>4.079</v>
       </c>
     </row>
     <row r="13">

--- a/downloads/FRB_H10_latest.xlsx
+++ b/downloads/FRB_H10_latest.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-12 to 2026-10-16</t>
+          <t>2026-10-19 to 2026-10-23</t>
         </is>
       </c>
     </row>
@@ -514,120 +514,141 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0.6981000000000001</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1.1209</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1.3306</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.5664</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>1.4093</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>94.93000000000001</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>4.08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.6984</v>
+        <v>0.7004</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1.1196</v>
+        <v>1.1232</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1.3255</v>
+        <v>1.3377</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.5616</v>
+        <v>0.5684</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.4214</v>
+        <v>1.4047</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>95.28</v>
+        <v>94.91</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>4.0839</v>
+        <v>4.0815</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.6956</v>
+        <v>0.7026</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1.1123</v>
+        <v>1.1219</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.3155</v>
+        <v>1.3391</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.5572</v>
+        <v>0.5692</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.4273</v>
+        <v>1.4063</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>95.15000000000001</v>
+        <v>94.45999999999999</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>4.081</v>
+        <v>4.0785</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.6914</v>
+        <v>0.702</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1.1204</v>
+        <v>1.1212</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1.3257</v>
+        <v>1.3381</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.5607</v>
+        <v>0.5682</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.4197</v>
+        <v>1.402</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>95.06</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>4.0799</v>
+        <v>4.0813</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.695</v>
+        <v>0.7037</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1.1231</v>
+        <v>1.1199</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.333</v>
+        <v>1.3375</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.5654</v>
+        <v>0.5705</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.4157</v>
+        <v>1.3993</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>94.95999999999999</v>
+        <v>94.94</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>4.079</v>
+        <v>4.0837</v>
       </c>
     </row>
     <row r="13">
